--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -956,53 +956,53 @@
     <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
+</t>
+  </si>
+  <si>
+    <t>Vaccin</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.realmCode</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.displayable</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.root</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.extension</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.templateId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeCode</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
+  </si>
+  <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Vaccin</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.realmCode</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.displayable</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.root</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.extension</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.templateId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeCode</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct
 </t>
   </si>
   <si>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
